--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260610.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260610.xlsx
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>4,052,678</t>
+          <t>2,825,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2,825,000</t>
+          <t>4,052,678</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>28,448,000</t>
+          <t>37,773,200</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>37,773,200</t>
+          <t>28,448,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
